--- a/docs/Mapping_casi_uso/cittadinanza/Citt_010.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_010.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="155">
   <si>
     <t>Sezione</t>
   </si>
@@ -377,7 +377,7 @@
     <t>comuneEstero</t>
   </si>
   <si>
-    <t>Atto collegato</t>
+    <t>Atto di nascita</t>
   </si>
   <si>
     <t>Id atto</t>
@@ -458,10 +458,25 @@
     <t>tipologia</t>
   </si>
   <si>
+    <t>Atto collegato di Cittadinanza</t>
+  </si>
+  <si>
+    <t>evento.eventoCollegatoCittadinanza</t>
+  </si>
+  <si>
     <t>Autorità mittente</t>
   </si>
   <si>
-    <t>evento.trascrizioneCittadinanza.autoritaMittente</t>
+    <t>Anagrafica Consolato</t>
+  </si>
+  <si>
+    <t>idAnagraficaConsolato</t>
+  </si>
+  <si>
+    <t>Anagrafica Consolato - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeAnagraficaConsolato</t>
   </si>
 </sst>
 </file>
@@ -520,13 +535,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="17.65234375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="45.0546875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="43.9609375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="28.44921875" customWidth="true" bestFit="true"/>
@@ -2055,22 +2070,22 @@
         <v>148</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68">
@@ -2078,22 +2093,22 @@
         <v>148</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69">
@@ -2101,22 +2116,22 @@
         <v>148</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70">
@@ -2124,22 +2139,22 @@
         <v>148</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71">
@@ -2147,7 +2162,7 @@
         <v>148</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>33</v>
@@ -2156,13 +2171,13 @@
         <v>149</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72">
@@ -2170,22 +2185,22 @@
         <v>148</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73">
@@ -2193,7 +2208,7 @@
         <v>148</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>33</v>
@@ -2202,12 +2217,403 @@
         <v>149</v>
       </c>
       <c r="E73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" s="2" t="s">
+      <c r="F88" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" s="2" t="s">
         <v>18</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/cittadinanza/Citt_010.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_010.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="156">
   <si>
     <t>Sezione</t>
   </si>
@@ -465,6 +465,9 @@
   </si>
   <si>
     <t>Autorità mittente</t>
+  </si>
+  <si>
+    <t>evento.trascrizioneCittadinanza.autoritaMittente</t>
   </si>
   <si>
     <t>Anagrafica Consolato</t>
@@ -541,7 +544,7 @@
     <col min="1" max="1" width="27.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="43.9609375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="45.0546875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="28.44921875" customWidth="true" bestFit="true"/>
@@ -2375,7 +2378,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>103</v>
@@ -2398,7 +2401,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>105</v>
@@ -2421,7 +2424,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>107</v>
@@ -2444,7 +2447,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>109</v>
@@ -2467,7 +2470,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>111</v>
@@ -2490,7 +2493,7 @@
         <v>33</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>113</v>
@@ -2513,7 +2516,7 @@
         <v>33</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>115</v>
@@ -2536,7 +2539,7 @@
         <v>33</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>117</v>
@@ -2559,7 +2562,7 @@
         <v>33</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>119</v>
@@ -2576,16 +2579,16 @@
         <v>150</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="E89" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2599,16 +2602,16 @@
         <v>150</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
